--- a/benchmark_results/problem3_smallest_epsilon/find_epsilon_benchmark_results.xlsx
+++ b/benchmark_results/problem3_smallest_epsilon/find_epsilon_benchmark_results.xlsx
@@ -7,11 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detailed_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary_Statistics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Oracle_Calls_by_Rule" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Runtime_by_Rule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Found_Epsilon_by_Rule" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,55 +456,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Largest_Epsilon_Heterogeneous</t>
+          <t>Oracle_Calls</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Oracle_Calls</t>
+          <t>Runtime_Seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Runtime_Seconds</t>
+          <t>Runtime_Minutes</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Runtime_Minutes</t>
+          <t>Dataset_Size</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Dataset_Size</t>
+          <t>Population_Utility</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Population_Utility</t>
+          <t>Violating_Subgroup</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Violating_Subgroup</t>
+          <t>Subgroup_Size</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Subgroup_Size</t>
+          <t>Subgroup_Utility</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Subgroup_Utility</t>
+          <t>Utility_Difference</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Utility_Difference</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Abs_Utility_Difference</t>
         </is>
@@ -529,49 +520,42 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>381575.63</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>84.047</v>
       </c>
       <c r="H2" t="n">
-        <v>27.525</v>
+        <v>1.401</v>
       </c>
       <c r="I2" t="n">
-        <v>0.459</v>
+        <v>35112</v>
       </c>
       <c r="J2" t="n">
-        <v>35112</v>
-      </c>
-      <c r="K2" t="n">
         <v>11626.77</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>{'Student': '1', 'HoursComputer': '2', 'Hobby': '1', 'GINI': '1', 'SexualOrientation': '1', 'FormalEducation': '4', 'RaceEthnicity': '1'}</t>
-        </is>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'DevType': '2', 'UndergradMajor': '2', 'SexualOrientation': '1', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2643</v>
       </c>
       <c r="M2" t="n">
-        <v>1367</v>
+        <v>-369948.87</v>
       </c>
       <c r="N2" t="n">
-        <v>148021.53</v>
+        <v>-381575.63</v>
       </c>
       <c r="O2" t="n">
-        <v>136394.76</v>
-      </c>
-      <c r="P2" t="n">
-        <v>136394.76</v>
+        <v>381575.63</v>
       </c>
     </row>
     <row r="3">
@@ -589,410 +573,1526 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>276890.91</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>33.526</v>
       </c>
       <c r="H3" t="n">
-        <v>11.627</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.194</v>
+        <v>35112</v>
       </c>
       <c r="J3" t="n">
-        <v>35112</v>
-      </c>
-      <c r="K3" t="n">
         <v>11626.77</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>{'GINI': '1', 'Student': '1'}</t>
-        </is>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'Dependents': '2', 'FormalEducation': '1', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3158</v>
       </c>
       <c r="M3" t="n">
-        <v>11220</v>
+        <v>-265264.15</v>
       </c>
       <c r="N3" t="n">
-        <v>-149012.01</v>
+        <v>-276890.91</v>
       </c>
       <c r="O3" t="n">
-        <v>-160638.78</v>
-      </c>
-      <c r="P3" t="n">
-        <v>160638.78</v>
+        <v>276890.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+          <t>{'Gender': 'Male'}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+          <t>{'Exercise': 'Daily or almost every day'}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>1500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>266326.93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>21.813</v>
       </c>
       <c r="H4" t="n">
-        <v>28.402</v>
+        <v>0.364</v>
       </c>
       <c r="I4" t="n">
-        <v>0.473</v>
+        <v>35112</v>
       </c>
       <c r="J4" t="n">
-        <v>35296</v>
-      </c>
-      <c r="K4" t="n">
-        <v>17285.53</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>{'Student': '1', 'Hobby': '1', 'HDI': '1', 'GINI': '2', 'Exercise': '4'}</t>
-        </is>
+        <v>11626.77</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': '1', 'GINI': '1', 'EducationParents': '3'}</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2743</v>
       </c>
       <c r="M4" t="n">
-        <v>2119</v>
+        <v>277953.69</v>
       </c>
       <c r="N4" t="n">
-        <v>183549.65</v>
+        <v>266326.93</v>
       </c>
       <c r="O4" t="n">
-        <v>166264.13</v>
-      </c>
-      <c r="P4" t="n">
-        <v>166264.13</v>
+        <v>266326.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+          <t>{'Gender': 'Male'}</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+          <t>{'Exercise': 'Daily or almost every day'}</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2000</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="E5" t="n">
+        <v>292424.99</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>14.42</v>
       </c>
       <c r="H5" t="n">
-        <v>13.159</v>
+        <v>0.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.219</v>
+        <v>35112</v>
       </c>
       <c r="J5" t="n">
+        <v>11626.77</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'GINI': '1', 'EducationParents': '2', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2253</v>
+      </c>
+      <c r="M5" t="n">
+        <v>304051.76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>292424.99</v>
+      </c>
+      <c r="O5" t="n">
+        <v>292424.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{'Gender': 'Male'}</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{'Exercise': 'Daily or almost every day'}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>272353.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.719</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35112</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11626.77</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'Age': '3', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>4955</v>
+      </c>
+      <c r="M6" t="n">
+        <v>283980.48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>272353.71</v>
+      </c>
+      <c r="O6" t="n">
+        <v>272353.71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{'Gender': 'Male'}</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{'Exercise': 'Daily or almost every day'}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>261215</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.967000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35112</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11626.77</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': '2', 'RaceEthnicity': '1', 'Continent': '1', 'SexualOrientation': '1', 'Hobby': '1', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4910</v>
+      </c>
+      <c r="M7" t="n">
+        <v>272841.76</v>
+      </c>
+      <c r="N7" t="n">
+        <v>261215</v>
+      </c>
+      <c r="O7" t="n">
+        <v>261215</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>318665.87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>88.175</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I8" t="n">
         <v>35296</v>
       </c>
-      <c r="K5" t="n">
+      <c r="J8" t="n">
         <v>17285.53</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>{'HoursComputer': '2', 'GINI': '1', 'Continent': '1', 'Age': '3'}</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3212</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-137544.28</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-154829.8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>154829.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total Experiments</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{'YearsCoding': '1', 'GINI': '1', 'Continent': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>501</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-301380.35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-318665.87</v>
+      </c>
+      <c r="O8" t="n">
+        <v>318665.87</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>400276.18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45.759</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="I9" t="n">
+        <v>35296</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17285.53</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'Dependents': '1', 'RaceEthnicity': '1', 'Hobby': '1', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1360</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-382990.66</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-400276.18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>400276.18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>492750.24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I10" t="n">
+        <v>35296</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17285.53</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{'Age': '1', 'Gender': '1', 'GINI': '1', 'RaceEthnicity': '1'}</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2478</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-475464.71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-492750.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>492750.24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>260501.83</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24.258</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="I11" t="n">
+        <v>35296</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17285.53</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'Gender': '1', 'RaceEthnicity': '1', 'GINI': '1', 'Age': '3'}</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3251</v>
+      </c>
+      <c r="M11" t="n">
+        <v>277787.36</v>
+      </c>
+      <c r="N11" t="n">
+        <v>260501.83</v>
+      </c>
+      <c r="O11" t="n">
+        <v>260501.83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2017457.48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20.722</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="I12" t="n">
+        <v>35296</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17285.53</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'Dependents': '2', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>7998</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2000171.96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2017457.48</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2017457.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': 'Straight or heterosexual'}</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2017457.48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.431</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I13" t="n">
+        <v>35296</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17285.53</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'Dependents': '2', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>7998</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-2000171.96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-2017457.48</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2017457.48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E14" t="n">
+        <v>423004.58</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="I14" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J14" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': '2', 'Dependents': '2', 'GINI': '1', 'RaceEthnicity': '1'}</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4808</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-379011.96</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-423004.58</v>
+      </c>
+      <c r="O14" t="n">
+        <v>423004.58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>894208.9399999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32.659</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="I15" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J15" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{'HDI': '1', 'GINI': '2', 'EducationParents': '1'}</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>3888</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-850216.3199999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-894208.9399999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>894208.9399999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>160283</v>
+      </c>
+      <c r="F16" t="n">
+        <v>26</v>
+      </c>
+      <c r="G16" t="n">
+        <v>545.436</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.090999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>{'SexualOrientation': '1', 'Hobby': '1', 'GINI': '1', 'Gender': '1'}</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>8683</v>
+      </c>
+      <c r="M16" t="n">
+        <v>204274.63</v>
+      </c>
+      <c r="N16" t="n">
+        <v>160282.01</v>
+      </c>
+      <c r="O16" t="n">
+        <v>160282.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>77426</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" t="n">
+        <v>241.544</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.026</v>
+      </c>
+      <c r="I17" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J17" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>{'HDI': '1', 'UndergradMajor': '2', 'GINI': '2', 'Gender': '1', 'SexualOrientation': '1'}</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>5971</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-33433.28</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-77425.89999999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>77425.89999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30729</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>113.843</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="I18" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J18" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>{'Hobby': '1', 'HDI': '1', 'GINI': '2'}</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>9657</v>
+      </c>
+      <c r="M18" t="n">
+        <v>13264.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-30728.32</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30728.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{'DevType': 'Engineering manager'}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>22137</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>85.467</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J19" t="n">
+        <v>43992.62</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>{'HDI': '1', 'Continent': '2'}</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>13264</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21856.37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-22136.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>22136.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Avg Runtime (seconds)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20.178</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Avg Oracle Calls</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Min Oracle Calls</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Max Oracle Calls</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total Runtime (minutes)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.345</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>500</v>
+      </c>
+      <c r="E20" t="n">
+        <v>947108.39</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>71.619</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': '1', 'GINI': '1', 'Continent': '1', 'DevType': '2'}</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2223</v>
+      </c>
+      <c r="M20" t="n">
+        <v>954186.97</v>
+      </c>
+      <c r="N20" t="n">
+        <v>947108.39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>947108.39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>1000</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="E21" t="n">
+        <v>319775.94</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24.989</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'DevType': '2', 'Gender': '1', 'SexualOrientation': '1', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3930</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-312697.36</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-319775.94</v>
+      </c>
+      <c r="O21" t="n">
+        <v>319775.94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E22" t="n">
+        <v>285673.03</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16.853</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': '4', 'Continent': '1', 'SexualOrientation': '1', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2758</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-278594.45</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-285673.03</v>
+      </c>
+      <c r="O22" t="n">
+        <v>285673.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>2000</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n">
+      <c r="E23" t="n">
+        <v>282501.78</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.573</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'Hobby': '1', 'Dependents': '2', 'GINI': '1', 'Age': '3'}</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2553</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-275423.2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-282501.78</v>
+      </c>
+      <c r="O23" t="n">
+        <v>282501.78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E24" t="n">
+        <v>458154.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.484</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="I24" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'DevType': '2', 'SexualOrientation': '1', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3506</v>
+      </c>
+      <c r="M24" t="n">
+        <v>465233.28</v>
+      </c>
+      <c r="N24" t="n">
+        <v>458154.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>458154.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{'RaceEthnicity': 'White or of European descent'}</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{'UndergradMajor': 'A natural science (ex. biology, chemistry, physics)'}</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>472720.68</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.127</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29496</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7078.58</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'DevType': '2', 'Gender': '1', 'GINI': '1', 'Student': '1'}</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3604</v>
+      </c>
+      <c r="M25" t="n">
+        <v>479799.27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>472720.68</v>
+      </c>
+      <c r="O25" t="n">
+        <v>472720.68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>500</v>
+      </c>
+      <c r="E26" t="n">
+        <v>333042.63</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>67.619</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>{'HDI': '1', 'HoursComputer': '2', 'DevType': '2', 'GINI': '2', 'Hobby': '1', 'Dependents': '2'}</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2091</v>
+      </c>
+      <c r="M26" t="n">
+        <v>359042.69</v>
+      </c>
+      <c r="N26" t="n">
+        <v>333042.63</v>
+      </c>
+      <c r="O26" t="n">
+        <v>333042.63</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>1000</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="E27" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>27.298</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="I27" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>{'Age': '3', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>6415</v>
+      </c>
+      <c r="M27" t="n">
+        <v>290309.39</v>
+      </c>
+      <c r="N27" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="O27" t="n">
+        <v>264309.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>264106.18</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24.077</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="I28" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J28" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{'GINI': '1', 'Gender': '1', 'HoursComputer': '2', 'DevType': '2'}</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>4116</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-238106.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-264106.18</v>
+      </c>
+      <c r="O28" t="n">
+        <v>264106.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>2000</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>27.525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11.627</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>28.402</v>
-      </c>
-      <c r="C3" t="n">
-        <v>13.159</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="E29" t="n">
+        <v>275301.27</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J29" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{'HoursComputer': '2', 'DevType': '2', 'Gender': '1', 'RaceEthnicity': '1', 'SexualOrientation': '1', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>3377</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-249301.21</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-275301.27</v>
+      </c>
+      <c r="O29" t="n">
+        <v>275301.27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E30" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12.724</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="I30" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J30" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{'Age': '3', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>6415</v>
+      </c>
+      <c r="M30" t="n">
+        <v>290309.39</v>
+      </c>
+      <c r="N30" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>264309.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{'Student': 'No'}</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{'FormalEducation': 'Other doctoral degree (Ph.D, Ed.D., etc.)'}</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>17.402</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I31" t="n">
+        <v>31715</v>
+      </c>
+      <c r="J31" t="n">
+        <v>26000.06</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{'Age': '3', 'GINI': '1'}</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>6415</v>
+      </c>
+      <c r="M31" t="n">
+        <v>290309.39</v>
+      </c>
+      <c r="N31" t="n">
+        <v>264309.33</v>
+      </c>
+      <c r="O31" t="n">
+        <v>264309.33</v>
       </c>
     </row>
   </sheetData>
